--- a/TestData/LV_TMTT0036857_VerifyTheFunctionalityOfDNDSharingFeatureForFRLOBOpportunityAndEngagementOnLightningView.xlsx
+++ b/TestData/LV_TMTT0036857_VerifyTheFunctionalityOfDNDSharingFeatureForFRLOBOpportunityAndEngagementOnLightningView.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D074861B-AAEA-47C2-AA7E-F8C1E9042E60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D84FC687-9F53-45C8-8A2E-BC16CF203F34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="548" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="548" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="StandardUser" sheetId="2" r:id="rId1"/>
@@ -163,9 +163,6 @@
     <t>Techno Coatings, Inc.</t>
   </si>
   <si>
-    <t>BUS - Business Services</t>
-  </si>
-  <si>
     <t>Dealership &amp; Rental Services</t>
   </si>
   <si>
@@ -317,6 +314,9 @@
   </si>
   <si>
     <t>System Administrator</t>
+  </si>
+  <si>
+    <t>Business Services</t>
   </si>
 </sst>
 </file>
@@ -658,14 +658,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -673,12 +673,12 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
@@ -692,12 +692,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{204DA895-5616-4092-9340-8DD85852997B}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -705,18 +705,18 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B2" t="s">
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -727,14 +727,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4767743C-3404-461F-B12D-D05F4986F9CF}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -742,26 +742,26 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B2" t="s">
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B3" t="s">
         <v>89</v>
-      </c>
-      <c r="B3" t="s">
-        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -772,17 +772,17 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0293C6CF-D2AF-4FB5-B989-23A4E6860FD2}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -795,24 +795,24 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D296AE2-31EA-40C7-99FB-9B7E70535054}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -824,9 +824,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18DA0E83-6177-407F-9158-15B7FDAAB4D9}">
   <dimension ref="A1:AF2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -912,19 +912,19 @@
         <v>36</v>
       </c>
       <c r="AC1" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AD1" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>85</v>
-      </c>
-      <c r="AE1" s="1" t="s">
-        <v>86</v>
       </c>
       <c r="AF1" s="1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>38</v>
       </c>
@@ -932,94 +932,94 @@
         <v>38</v>
       </c>
       <c r="C2" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F2" t="s">
+        <v>40</v>
+      </c>
+      <c r="G2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H2" t="s">
+        <v>41</v>
+      </c>
+      <c r="I2" t="s">
+        <v>40</v>
+      </c>
+      <c r="J2" t="s">
+        <v>40</v>
+      </c>
+      <c r="K2" t="s">
+        <v>64</v>
+      </c>
+      <c r="L2" t="s">
+        <v>42</v>
+      </c>
+      <c r="M2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N2" t="s">
         <v>79</v>
       </c>
-      <c r="D2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="O2" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="R2" t="s">
+        <v>45</v>
+      </c>
+      <c r="S2" t="s">
+        <v>45</v>
+      </c>
+      <c r="T2" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="U2" t="s">
+        <v>47</v>
+      </c>
+      <c r="V2" t="s">
+        <v>48</v>
+      </c>
+      <c r="W2" t="s">
+        <v>49</v>
+      </c>
+      <c r="X2" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>51</v>
+      </c>
+      <c r="AA2" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AB2" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>82</v>
+      </c>
+      <c r="AD2" t="s">
         <v>40</v>
       </c>
-      <c r="F2" t="s">
-        <v>41</v>
-      </c>
-      <c r="G2" t="s">
-        <v>41</v>
-      </c>
-      <c r="H2" t="s">
-        <v>42</v>
-      </c>
-      <c r="I2" t="s">
-        <v>41</v>
-      </c>
-      <c r="J2" t="s">
-        <v>41</v>
-      </c>
-      <c r="K2" t="s">
-        <v>65</v>
-      </c>
-      <c r="L2" t="s">
-        <v>43</v>
-      </c>
-      <c r="M2" t="s">
-        <v>44</v>
-      </c>
-      <c r="N2" t="s">
-        <v>80</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q2" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="R2" t="s">
-        <v>46</v>
-      </c>
-      <c r="S2" t="s">
-        <v>46</v>
-      </c>
-      <c r="T2" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="U2" t="s">
-        <v>48</v>
-      </c>
-      <c r="V2" t="s">
-        <v>49</v>
-      </c>
-      <c r="W2" t="s">
-        <v>50</v>
-      </c>
-      <c r="X2" t="s">
-        <v>51</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>81</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>52</v>
-      </c>
-      <c r="AA2" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AB2" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>83</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>41</v>
-      </c>
       <c r="AE2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AF2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -1030,39 +1030,39 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFD3AFCB-FF3D-4430-A7EF-EB1CDD64D866}">
   <dimension ref="A1:A6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
         <v>77</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A6" s="4" t="s">
-        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -1073,68 +1073,68 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F2CDCD2-7F5E-40FD-BAB3-4BCEC31CD21E}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>54</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>55</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="H1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B2" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>60</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>61</v>
-      </c>
-      <c r="D2" t="s">
-        <v>62</v>
       </c>
       <c r="E2" t="s">
         <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G2" t="s">
         <v>10</v>
       </c>
       <c r="H2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -1145,26 +1145,26 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C2F5355-6C7D-4D28-98E4-51F296DA7AFE}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/LV_TMTT0036857_VerifyTheFunctionalityOfDNDSharingFeatureForFRLOBOpportunityAndEngagementOnLightningView.xlsx
+++ b/TestData/LV_TMTT0036857_VerifyTheFunctionalityOfDNDSharingFeatureForFRLOBOpportunityAndEngagementOnLightningView.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27425"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D84FC687-9F53-45C8-8A2E-BC16CF203F34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FE54858-F9D8-4EF5-8626-7C53D0902289}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="548" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="548" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="StandardUser" sheetId="2" r:id="rId1"/>
@@ -55,9 +55,6 @@
     <t>Profile</t>
   </si>
   <si>
-    <t>CF Financial User</t>
-  </si>
-  <si>
     <t>App Name</t>
   </si>
   <si>
@@ -241,9 +238,6 @@
     <t>LA</t>
   </si>
   <si>
-    <t>William Peluchiwski</t>
-  </si>
-  <si>
     <t>Eric Cartier</t>
   </si>
   <si>
@@ -317,6 +311,12 @@
   </si>
   <si>
     <t>Business Services</t>
+  </si>
+  <si>
+    <t>Eric Winthrop</t>
+  </si>
+  <si>
+    <t>FR Financial User</t>
   </si>
 </sst>
 </file>
@@ -673,15 +673,15 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>65</v>
+        <v>89</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -694,7 +694,7 @@
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -705,18 +705,18 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -742,26 +742,26 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -779,12 +779,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -802,17 +802,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -828,198 +828,198 @@
   <sheetData>
     <row r="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="R1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="U1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="Z1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AF1" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="AC1" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="AE1" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="AF1" s="1" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E2" t="s">
         <v>38</v>
       </c>
-      <c r="B2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C2" s="5" t="s">
+      <c r="F2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2" t="s">
+        <v>39</v>
+      </c>
+      <c r="H2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I2" t="s">
+        <v>39</v>
+      </c>
+      <c r="J2" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2" t="s">
+        <v>63</v>
+      </c>
+      <c r="L2" t="s">
+        <v>41</v>
+      </c>
+      <c r="M2" t="s">
+        <v>42</v>
+      </c>
+      <c r="N2" t="s">
+        <v>77</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="R2" t="s">
+        <v>44</v>
+      </c>
+      <c r="S2" t="s">
+        <v>44</v>
+      </c>
+      <c r="T2" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="U2" t="s">
+        <v>46</v>
+      </c>
+      <c r="V2" t="s">
+        <v>47</v>
+      </c>
+      <c r="W2" t="s">
+        <v>48</v>
+      </c>
+      <c r="X2" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y2" t="s">
         <v>78</v>
       </c>
-      <c r="D2" t="s">
-        <v>90</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="Z2" t="s">
+        <v>50</v>
+      </c>
+      <c r="AA2" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB2" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>80</v>
+      </c>
+      <c r="AD2" t="s">
         <v>39</v>
       </c>
-      <c r="F2" t="s">
-        <v>40</v>
-      </c>
-      <c r="G2" t="s">
-        <v>40</v>
-      </c>
-      <c r="H2" t="s">
-        <v>41</v>
-      </c>
-      <c r="I2" t="s">
-        <v>40</v>
-      </c>
-      <c r="J2" t="s">
-        <v>40</v>
-      </c>
-      <c r="K2" t="s">
-        <v>64</v>
-      </c>
-      <c r="L2" t="s">
-        <v>42</v>
-      </c>
-      <c r="M2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N2" t="s">
-        <v>79</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q2" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="R2" t="s">
-        <v>45</v>
-      </c>
-      <c r="S2" t="s">
-        <v>45</v>
-      </c>
-      <c r="T2" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="U2" t="s">
-        <v>47</v>
-      </c>
-      <c r="V2" t="s">
-        <v>48</v>
-      </c>
-      <c r="W2" t="s">
-        <v>49</v>
-      </c>
-      <c r="X2" t="s">
-        <v>50</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>80</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>51</v>
-      </c>
-      <c r="AA2" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AB2" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>82</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>40</v>
-      </c>
       <c r="AE2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AF2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -1037,7 +1037,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
@@ -1047,22 +1047,22 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -1087,54 +1087,54 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>57</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2" t="s">
         <v>59</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>60</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" t="s">
         <v>61</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" t="s">
-        <v>63</v>
-      </c>
-      <c r="G2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H2" t="s">
-        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -1153,18 +1153,18 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B2" t="s">
         <v>73</v>
-      </c>
-      <c r="B2" t="s">
-        <v>75</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/LV_TMTT0036857_VerifyTheFunctionalityOfDNDSharingFeatureForFRLOBOpportunityAndEngagementOnLightningView.xlsx
+++ b/TestData/LV_TMTT0036857_VerifyTheFunctionalityOfDNDSharingFeatureForFRLOBOpportunityAndEngagementOnLightningView.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27531"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FE54858-F9D8-4EF5-8626-7C53D0902289}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18D63793-10EC-46B6-91A0-E2CB35CC5177}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="548" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="548" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="StandardUser" sheetId="2" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="92">
   <si>
     <t>James Craven</t>
   </si>
@@ -317,13 +317,16 @@
   </si>
   <si>
     <t>FR Financial User</t>
+  </si>
+  <si>
+    <t>Matthew Bertolatus</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -341,6 +344,13 @@
     </font>
     <font>
       <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -366,7 +376,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -377,6 +387,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1029,38 +1042,42 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFD3AFCB-FF3D-4430-A7EF-EB1CDD64D866}">
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>91</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>75</v>
       </c>

--- a/TestData/LV_TMTT0036857_VerifyTheFunctionalityOfDNDSharingFeatureForFRLOBOpportunityAndEngagementOnLightningView.xlsx
+++ b/TestData/LV_TMTT0036857_VerifyTheFunctionalityOfDNDSharingFeatureForFRLOBOpportunityAndEngagementOnLightningView.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18D63793-10EC-46B6-91A0-E2CB35CC5177}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DC09258-8C61-41D5-BC96-C8914BB5FB3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="548" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="548" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="StandardUser" sheetId="2" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="93">
   <si>
     <t>James Craven</t>
   </si>
@@ -320,6 +320,9 @@
   </si>
   <si>
     <t>Matthew Bertolatus</t>
+  </si>
+  <si>
+    <t>Andy Chen</t>
   </si>
 </sst>
 </file>
@@ -671,14 +674,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -689,7 +692,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>89</v>
       </c>
@@ -705,12 +708,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{204DA895-5616-4092-9340-8DD85852997B}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -721,7 +724,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>84</v>
       </c>
@@ -740,14 +743,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4767743C-3404-461F-B12D-D05F4986F9CF}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -758,7 +761,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>67</v>
       </c>
@@ -769,7 +772,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>86</v>
       </c>
@@ -785,17 +788,17 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0293C6CF-D2AF-4FB5-B989-23A4E6860FD2}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -808,22 +811,22 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D296AE2-31EA-40C7-99FB-9B7E70535054}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>85</v>
       </c>
@@ -837,9 +840,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18DA0E83-6177-407F-9158-15B7FDAAB4D9}">
   <dimension ref="A1:AF2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -937,7 +940,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>37</v>
       </c>
@@ -978,7 +981,7 @@
         <v>42</v>
       </c>
       <c r="N2" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="O2" s="3" t="s">
         <v>43</v>
@@ -1043,33 +1046,33 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFD3AFCB-FF3D-4430-A7EF-EB1CDD64D866}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.88671875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>91</v>
       </c>
@@ -1077,7 +1080,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>75</v>
       </c>
@@ -1090,19 +1093,19 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F2CDCD2-7F5E-40FD-BAB3-4BCEC31CD21E}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>51</v>
       </c>
@@ -1128,7 +1131,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>47</v>
       </c>
@@ -1162,13 +1165,13 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C2F5355-6C7D-4D28-98E4-51F296DA7AFE}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>72</v>
       </c>
@@ -1176,7 +1179,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>71</v>
       </c>

--- a/TestData/LV_TMTT0036857_VerifyTheFunctionalityOfDNDSharingFeatureForFRLOBOpportunityAndEngagementOnLightningView.xlsx
+++ b/TestData/LV_TMTT0036857_VerifyTheFunctionalityOfDNDSharingFeatureForFRLOBOpportunityAndEngagementOnLightningView.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27726"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DC09258-8C61-41D5-BC96-C8914BB5FB3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72F72493-EF8A-4B66-951E-D72E39799599}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="548" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="548" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="StandardUser" sheetId="2" r:id="rId1"/>
@@ -82,9 +82,6 @@
     <t>JobType</t>
   </si>
   <si>
-    <t>IndustryGroup</t>
-  </si>
-  <si>
     <t>Sector</t>
   </si>
   <si>
@@ -310,9 +307,6 @@
     <t>System Administrator</t>
   </si>
   <si>
-    <t>Business Services</t>
-  </si>
-  <si>
     <t>Eric Winthrop</t>
   </si>
   <si>
@@ -323,6 +317,12 @@
   </si>
   <si>
     <t>Andy Chen</t>
+  </si>
+  <si>
+    <t>IndustryGroup/HLSector</t>
+  </si>
+  <si>
+    <t>CSDN-0000007327</t>
   </si>
 </sst>
 </file>
@@ -689,15 +689,15 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -721,18 +721,18 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B2" t="s">
         <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -758,26 +758,26 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B2" t="s">
         <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B3" t="s">
         <v>86</v>
-      </c>
-      <c r="B3" t="s">
-        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -828,7 +828,7 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -853,189 +853,189 @@
         <v>11</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="R1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="U1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>33</v>
       </c>
       <c r="Z1" s="1" t="s">
         <v>11</v>
       </c>
       <c r="AA1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AB1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="AF1" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="AC1" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="AE1" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="AF1" s="1" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="D2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E2" t="s">
         <v>37</v>
       </c>
-      <c r="B2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C2" s="5" t="s">
+      <c r="F2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H2" t="s">
+        <v>39</v>
+      </c>
+      <c r="I2" t="s">
+        <v>38</v>
+      </c>
+      <c r="J2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K2" t="s">
+        <v>62</v>
+      </c>
+      <c r="L2" t="s">
+        <v>40</v>
+      </c>
+      <c r="M2" t="s">
+        <v>41</v>
+      </c>
+      <c r="N2" t="s">
+        <v>90</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="R2" t="s">
+        <v>43</v>
+      </c>
+      <c r="S2" t="s">
+        <v>43</v>
+      </c>
+      <c r="T2" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="U2" t="s">
+        <v>45</v>
+      </c>
+      <c r="V2" t="s">
+        <v>46</v>
+      </c>
+      <c r="W2" t="s">
+        <v>47</v>
+      </c>
+      <c r="X2" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>77</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA2" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB2" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>79</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AF2" t="s">
         <v>76</v>
-      </c>
-      <c r="D2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F2" t="s">
-        <v>39</v>
-      </c>
-      <c r="G2" t="s">
-        <v>39</v>
-      </c>
-      <c r="H2" t="s">
-        <v>40</v>
-      </c>
-      <c r="I2" t="s">
-        <v>39</v>
-      </c>
-      <c r="J2" t="s">
-        <v>39</v>
-      </c>
-      <c r="K2" t="s">
-        <v>63</v>
-      </c>
-      <c r="L2" t="s">
-        <v>41</v>
-      </c>
-      <c r="M2" t="s">
-        <v>42</v>
-      </c>
-      <c r="N2" t="s">
-        <v>92</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q2" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="R2" t="s">
-        <v>44</v>
-      </c>
-      <c r="S2" t="s">
-        <v>44</v>
-      </c>
-      <c r="T2" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="U2" t="s">
-        <v>46</v>
-      </c>
-      <c r="V2" t="s">
-        <v>47</v>
-      </c>
-      <c r="W2" t="s">
-        <v>48</v>
-      </c>
-      <c r="X2" t="s">
-        <v>49</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>78</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>50</v>
-      </c>
-      <c r="AA2" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB2" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>80</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>39</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>39</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -1054,7 +1054,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
@@ -1064,25 +1064,25 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -1107,54 +1107,54 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>53</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>56</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C2" t="s">
         <v>58</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>59</v>
-      </c>
-      <c r="D2" t="s">
-        <v>60</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G2" t="s">
         <v>9</v>
       </c>
       <c r="H2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -1173,7 +1173,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>7</v>
@@ -1181,10 +1181,10 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/LV_TMTT0036857_VerifyTheFunctionalityOfDNDSharingFeatureForFRLOBOpportunityAndEngagementOnLightningView.xlsx
+++ b/TestData/LV_TMTT0036857_VerifyTheFunctionalityOfDNDSharingFeatureForFRLOBOpportunityAndEngagementOnLightningView.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72F72493-EF8A-4B66-951E-D72E39799599}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4912349C-B1E4-4874-B70D-0EE40D8A0BF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="548" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="548" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="StandardUser" sheetId="2" r:id="rId1"/>
@@ -322,7 +322,7 @@
     <t>IndustryGroup/HLSector</t>
   </si>
   <si>
-    <t>CSDN-0000007327</t>
+    <t>CSDN-0000002536</t>
   </si>
 </sst>
 </file>
@@ -674,14 +674,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -692,7 +692,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>87</v>
       </c>
@@ -708,12 +708,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{204DA895-5616-4092-9340-8DD85852997B}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -724,7 +724,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>83</v>
       </c>
@@ -743,14 +743,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4767743C-3404-461F-B12D-D05F4986F9CF}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -761,7 +761,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>66</v>
       </c>
@@ -772,7 +772,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>85</v>
       </c>
@@ -788,17 +788,17 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0293C6CF-D2AF-4FB5-B989-23A4E6860FD2}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -811,22 +811,22 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D296AE2-31EA-40C7-99FB-9B7E70535054}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>84</v>
       </c>
@@ -840,9 +840,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18DA0E83-6177-407F-9158-15B7FDAAB4D9}">
   <dimension ref="A1:AF2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -940,7 +940,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>36</v>
       </c>
@@ -1046,33 +1046,33 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFD3AFCB-FF3D-4430-A7EF-EB1CDD64D866}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>89</v>
       </c>
@@ -1080,7 +1080,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>74</v>
       </c>
@@ -1093,19 +1093,19 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F2CDCD2-7F5E-40FD-BAB3-4BCEC31CD21E}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>50</v>
       </c>
@@ -1131,7 +1131,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>46</v>
       </c>
@@ -1165,13 +1165,13 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C2F5355-6C7D-4D28-98E4-51F296DA7AFE}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>71</v>
       </c>
@@ -1179,7 +1179,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>70</v>
       </c>
